--- a/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0001T0006Z000C1N196_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0001T0006Z000C1N196_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>13.3846865897549</v>
+        <v>2.175011570835171</v>
       </c>
       <c r="D2" t="n">
-        <v>11.51980280112214</v>
+        <v>1.871967955182347</v>
       </c>
       <c r="E2" t="n">
-        <v>11.97512236796809</v>
+        <v>1.945957384794815</v>
       </c>
       <c r="F2" t="n">
-        <v>23.35521409831153</v>
+        <v>3.795222290975623</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>38.35488815123284</v>
+        <v>6.232669324575337</v>
       </c>
       <c r="D3" t="n">
-        <v>68.35705103617994</v>
+        <v>11.10802079337924</v>
       </c>
       <c r="E3" t="n">
-        <v>11.97512236796809</v>
+        <v>1.945957384794815</v>
       </c>
       <c r="F3" t="n">
-        <v>23.35521409831153</v>
+        <v>3.795222290975623</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>25.8940147524481</v>
+        <v>4.207777397272817</v>
       </c>
       <c r="D4" t="n">
-        <v>24.4757230640219</v>
+        <v>3.977304997903558</v>
       </c>
       <c r="E4" t="n">
-        <v>11.97512236796809</v>
+        <v>1.945957384794815</v>
       </c>
       <c r="F4" t="n">
-        <v>23.35521409831153</v>
+        <v>3.795222290975623</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>22.88087405375997</v>
+        <v>3.718142033735996</v>
       </c>
       <c r="D5" t="n">
-        <v>29.259226230933</v>
+        <v>4.754624262526613</v>
       </c>
       <c r="E5" t="n">
-        <v>11.97512236796809</v>
+        <v>1.945957384794815</v>
       </c>
       <c r="F5" t="n">
-        <v>23.35521409831153</v>
+        <v>3.795222290975623</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>15.49410373684909</v>
+        <v>2.517791857237976</v>
       </c>
       <c r="D6" t="n">
-        <v>15.28800077285085</v>
+        <v>2.484300125588263</v>
       </c>
       <c r="E6" t="n">
-        <v>11.97512236796809</v>
+        <v>1.945957384794815</v>
       </c>
       <c r="F6" t="n">
-        <v>23.35521409831153</v>
+        <v>3.795222290975623</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>22.997656886786</v>
+        <v>3.737119244102726</v>
       </c>
       <c r="D7" t="n">
-        <v>16.47313225399</v>
+        <v>2.676883991273375</v>
       </c>
       <c r="E7" t="n">
-        <v>11.97512236796809</v>
+        <v>1.945957384794815</v>
       </c>
       <c r="F7" t="n">
-        <v>23.35521409831153</v>
+        <v>3.795222290975623</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>21.30890055719749</v>
+        <v>3.462696340544592</v>
       </c>
       <c r="D8" t="n">
-        <v>35.40587087628788</v>
+        <v>5.753454017396781</v>
       </c>
       <c r="E8" t="n">
-        <v>11.97512236796809</v>
+        <v>1.945957384794815</v>
       </c>
       <c r="F8" t="n">
-        <v>23.35521409831153</v>
+        <v>3.795222290975623</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>8.904693489433507</v>
+        <v>1.447012692032945</v>
       </c>
       <c r="D9" t="n">
-        <v>5.431349055701268</v>
+        <v>0.8825942215514562</v>
       </c>
       <c r="E9" t="n">
-        <v>11.97512236796809</v>
+        <v>1.945957384794815</v>
       </c>
       <c r="F9" t="n">
-        <v>23.35521409831153</v>
+        <v>3.795222290975623</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>9.938712535840155</v>
+        <v>1.615040787074025</v>
       </c>
       <c r="D10" t="n">
-        <v>10.50859098224228</v>
+        <v>1.707646034614371</v>
       </c>
       <c r="E10" t="n">
-        <v>11.97512236796809</v>
+        <v>1.945957384794815</v>
       </c>
       <c r="F10" t="n">
-        <v>23.35521409831153</v>
+        <v>3.795222290975623</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>17.85863250077135</v>
+        <v>2.902027781375345</v>
       </c>
       <c r="D11" t="n">
-        <v>15.93322670532155</v>
+        <v>2.589149339614751</v>
       </c>
       <c r="E11" t="n">
-        <v>11.97512236796809</v>
+        <v>1.945957384794815</v>
       </c>
       <c r="F11" t="n">
-        <v>23.35521409831153</v>
+        <v>3.795222290975623</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>51.07324671030437</v>
+        <v>8.29940259042446</v>
       </c>
       <c r="D12" t="n">
-        <v>80.70894967737279</v>
+        <v>13.11520432257308</v>
       </c>
       <c r="E12" t="n">
-        <v>11.97512236796809</v>
+        <v>1.945957384794815</v>
       </c>
       <c r="F12" t="n">
-        <v>23.35521409831153</v>
+        <v>3.795222290975623</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
